--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8385" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8385" uniqueCount="306">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Entry in the bundle - will have a resource or information</t>
@@ -908,6 +908,9 @@
   </si>
   <si>
     <t>practitionerRole</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">PractitionerRole {http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE}
@@ -17228,10 +17231,10 @@
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="F145" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>74</v>
@@ -17905,13 +17908,13 @@
         <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -20749,7 +20752,7 @@
         <v>170</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>74</v>
@@ -21433,13 +21436,13 @@
         <v>74</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
@@ -21502,13 +21505,13 @@
         <v>74</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>74</v>
@@ -24277,7 +24280,7 @@
         <v>170</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C209" t="s" s="2">
         <v>74</v>
@@ -24961,13 +24964,13 @@
         <v>74</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
@@ -25030,13 +25033,13 @@
         <v>74</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ215" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>74</v>
@@ -27802,7 +27805,7 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B241" s="2"/>
       <c r="C241" t="s" s="2">
@@ -27825,19 +27828,19 @@
         <v>83</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O241" t="s" s="2">
         <v>74</v>
@@ -27886,7 +27889,7 @@
         <v>74</v>
       </c>
       <c r="AE241" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AF241" t="s" s="2">
         <v>75</v>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>Entry in the bundle - will have a resource or information</t>
@@ -891,6 +891,9 @@
     <t>practitioner</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Practitioner {http://minsal.cl/listaespera/StructureDefinition/PractitionerLE}
 </t>
   </si>
@@ -908,9 +911,6 @@
   </si>
   <si>
     <t>practitionerRole</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">PractitionerRole {http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE}
@@ -13703,10 +13703,10 @@
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>74</v>
@@ -14380,13 +14380,13 @@
         <v>74</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -14452,10 +14452,10 @@
         <v>265</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>74</v>
@@ -17224,17 +17224,17 @@
         <v>170</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F145" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>74</v>
@@ -17980,10 +17980,10 @@
         <v>265</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>74</v>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleAgendarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
